--- a/templates/SHAW_onboarding.xlsx
+++ b/templates/SHAW_onboarding.xlsx
@@ -12,69 +12,70 @@
     <sheet name="OutputFiles" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="MultiRecord_ATOCTRAN" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="MultiRecord_TRANERT" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Reconciliation_TRANERT" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="COLLATERAL_MASTER_Mapping" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="FEE_MASTER_Mapping" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="LOAN_MASTER_Mapping" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="LOANS_NAME_Mapping" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="POSTED_TRANS_Mapping" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="TRANS_MASTER_Mapping" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="ATOCTRAN_100_Mapping" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ATOCTRAN_100_Rules" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="ATOCTRAN_200_Mapping" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="ATOCTRAN_200_Rules" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ATOCTRAN_300_Mapping" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="ATOCTRAN_300_Rules" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="ATOCTRAN_605_Mapping" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="ATOCTRAN_605_Rules" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="ATOCTRAN_700_Mapping" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="ATOCTRAN_700_Rules" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="ATOCTRAN_900_Mapping" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="ATOCTRAN_900_Rules" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="ATOCTRAN_060_Mapping" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="ATOCTRAN_060_Rules" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="CDSTRANS_EAC_COLLATERAL_Mapping" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="CDSTRANS_EAC_COLLATERAL_Rules" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="CDSTRANS_EFB_Mapping" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="CDSTRANS_EFB_Rules" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="CDSTRANS_EFI_Mapping" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="CDSTRANS_EFI_Rules" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="CDSTRANS_EF~FEE_WAIVERS_Mapping" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="CDSTRANS_EFW_FEE_WAIVERS_Rules" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="CDSTRANS_EFX_Mapping" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="CDSTRANS_EFX_Rules" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="CDSTRANS_ESA_Mapping" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="CDSTRANS_ESA_Rules" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="CDSTRANS_EST_Mapping" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="CDSTRANS_EST_Rules" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="CDSTRANS_HSS_Mapping" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="CDSTRANS_HSS_Rules" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="CDSTRANS_RLT_Mapping" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="CDSTRANS_RLT_Rules" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="CDSTRANS_SEC_Mapping" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="CDSTRANS_SEC_Rules" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="CDSTRANS_XPR_Mapping" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="CDSTRANS_XPR_Rules" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="CONTACT_Mapping" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="CONTACT_Rules" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="CONTACT_ACCOUNT_Mapping" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="CONTACT_ACCOUNT_Rules" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="P327_Mapping" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="P327_Rules" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="TRANERT_BATCH_HEADER_Mapping" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet name="TRANERT_BATCH_HEADER_Rules" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet name="TRANERT_NEW1_Mapping" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet name="TRANERT_NEW1_Rules" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet name="TRANERT_CUS_Mapping" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="TRANERT_CUS_Rules" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet name="TRANERT_ORI_Mapping" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet name="TRANERT_ORI_Rules" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet name="TRANERT_COD_Mapping" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet name="TRANERT_COD_Rules" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet name="TRANERT_CBRS_Mapping" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet name="TRANERT_CBRS_Rules" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet name="TRANERT_REC_Mapping" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet name="TRANERT_REC_Rules" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="CrossTypeRules_TRANERT" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Reconciliation_TRANERT" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="COLLATERAL_MASTER_Mapping" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="FEE_MASTER_Mapping" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="LOAN_MASTER_Mapping" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="LOANS_NAME_Mapping" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="POSTED_TRANS_Mapping" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="TRANS_MASTER_Mapping" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ATOCTRAN_100_Mapping" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ATOCTRAN_100_Rules" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="ATOCTRAN_200_Mapping" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="ATOCTRAN_200_Rules" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="ATOCTRAN_300_Mapping" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="ATOCTRAN_300_Rules" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="ATOCTRAN_605_Mapping" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="ATOCTRAN_605_Rules" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="ATOCTRAN_700_Mapping" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="ATOCTRAN_700_Rules" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="ATOCTRAN_900_Mapping" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="ATOCTRAN_900_Rules" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="ATOCTRAN_060_Mapping" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="ATOCTRAN_060_Rules" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="CDSTRANS_EAC_COLLATERAL_Mapping" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="CDSTRANS_EAC_COLLATERAL_Rules" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="CDSTRANS_EFB_Mapping" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="CDSTRANS_EFB_Rules" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="CDSTRANS_EFI_Mapping" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="CDSTRANS_EFI_Rules" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="CDSTRANS_EF~FEE_WAIVERS_Mapping" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="CDSTRANS_EFW_FEE_WAIVERS_Rules" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="CDSTRANS_EFX_Mapping" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="CDSTRANS_EFX_Rules" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="CDSTRANS_ESA_Mapping" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="CDSTRANS_ESA_Rules" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="CDSTRANS_EST_Mapping" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="CDSTRANS_EST_Rules" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="CDSTRANS_HSS_Mapping" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="CDSTRANS_HSS_Rules" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="CDSTRANS_RLT_Mapping" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="CDSTRANS_RLT_Rules" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="CDSTRANS_SEC_Mapping" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="CDSTRANS_SEC_Rules" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="CDSTRANS_XPR_Mapping" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="CDSTRANS_XPR_Rules" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="CONTACT_Mapping" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="CONTACT_Rules" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="CONTACT_ACCOUNT_Mapping" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="CONTACT_ACCOUNT_Rules" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="P327_Mapping" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="P327_Rules" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="TRANERT_BATCH_HEADER_Mapping" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="TRANERT_BATCH_HEADER_Rules" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="TRANERT_NEW1_Mapping" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="TRANERT_NEW1_Rules" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="TRANERT_CUS_Mapping" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="TRANERT_CUS_Rules" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="TRANERT_ORI_Mapping" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="TRANERT_ORI_Rules" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="TRANERT_COD_Mapping" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="TRANERT_COD_Rules" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="TRANERT_CBRS_Mapping" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="TRANERT_CBRS_Rules" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="TRANERT_REC_Mapping" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="TRANERT_REC_Rules" sheetId="69" state="visible" r:id="rId69"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -743,7 +744,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TODO_FIELD_1_LOANS_NAME</t>
+          <t>TODO_FIELD_1_LOAN_MASTER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -772,7 +773,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>TODO(mapping-pending): LOANS_NAME layout not yet authored. Replace this row with real fields before onboarding.</t>
+          <t>TODO(mapping-pending): LOAN_MASTER layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
     </row>
@@ -857,7 +858,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TODO_FIELD_1_POSTED_TRANS</t>
+          <t>TODO_FIELD_1_LOANS_NAME</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -886,7 +887,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>TODO(mapping-pending): POSTED_TRANS layout not yet authored. Replace this row with real fields before onboarding.</t>
+          <t>TODO(mapping-pending): LOANS_NAME layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
     </row>
@@ -971,7 +972,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TODO_FIELD_1_TRANS_MASTER</t>
+          <t>TODO_FIELD_1_POSTED_TRANS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1000,7 +1001,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>TODO(mapping-pending): TRANS_MASTER layout not yet authored. Replace this row with real fields before onboarding.</t>
+          <t>TODO(mapping-pending): POSTED_TRANS layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
     </row>
@@ -1010,6 +1011,120 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Target Name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Valid Values</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TODO_FIELD_1_TRANS_MASTER</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>todo_field_1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TODO(mapping-pending): TRANS_MASTER layout not yet authored. Replace this row with real fields before onboarding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1323,7 +1438,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1873,7 +1988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2319,7 +2434,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2995,7 +3110,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3777,7 +3892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4761,412 +4876,6 @@
       <c r="H24" t="inlineStr">
         <is>
           <t>000</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Field Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Target Name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Transformation</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Valid Values</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LOCATION-CODE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>location_code</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Create this record only for accounts that came in 090 record (i.e. MAS) of ctoatran.txt delta file AND ACTG-SYS-ID (in ctoatran master) NOT EQUAL TO ('CAS' or 'CASW') Hard-code to 100030</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100030</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Location Code for Account</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ACCT-NUM</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>acct_num</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Txn Type 605 is created only for manually set up accounts i.e. for accounts for which CCI = 1; AND for accounts present in 090 txn (latest ctoatran delta file) Create just one 605 record per account; If there are more than one Contacts for an account then Create just one 605 record and that is for a Primary Contact. ACCT-NUM = BR + CUS + LN</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Account Number</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TRANSACTION-CODE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>transaction_code</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Default to '605'</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Type of Transaction</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TRANSACTION-DATE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>transaction_date</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>CCYYMMDD</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Default to &lt;Batch Date&gt;</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>&lt;Batch</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Date of Transaction</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NEW-PORTFOLIO-LOCATION-CODE</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>new_portfolio_location_code</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Default to 200000</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>If the Account is in a Location that uses Customer Portfolio processing, the ...</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NEW-PORTFOLIO-ID</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>new_portfolio_id</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Select CONTACT-ID from contact-account.txt where ACCT-NUM = ILMAST-KEY AND NAME-RELATIONSHIP = 'A' [since we need to create only one Transaction 200 and that's for Primary Account holder]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>If the Account is in a Location that uses Customer Portfolio processing, the ...</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NEW-PORTFOLIO-CONTACT-ID</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>new_portfolio_contact_id</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Select CONTACT-ID from contact-account.txt where ACCT-NUM = ILMAST-KEY AND NAME-RELATIONSHIP = 'A' [since we need to create only one Transaction 200 and that's for Primary Account holder]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>If the Account is in a Location that uses Customer Portfolio processing, the ...</t>
         </is>
       </c>
     </row>
@@ -5367,6 +5076,412 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Target Name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Valid Values</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LOCATION-CODE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>location_code</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Create this record only for accounts that came in 090 record (i.e. MAS) of ctoatran.txt delta file AND ACTG-SYS-ID (in ctoatran master) NOT EQUAL TO ('CAS' or 'CASW') Hard-code to 100030</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100030</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Location Code for Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACCT-NUM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>acct_num</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Txn Type 605 is created only for manually set up accounts i.e. for accounts for which CCI = 1; AND for accounts present in 090 txn (latest ctoatran delta file) Create just one 605 record per account; If there are more than one Contacts for an account then Create just one 605 record and that is for a Primary Contact. ACCT-NUM = BR + CUS + LN</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Account Number</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TRANSACTION-CODE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>transaction_code</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Default to '605'</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Type of Transaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TRANSACTION-DATE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>transaction_date</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CCYYMMDD</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Default to &lt;Batch Date&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>&lt;Batch</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Date of Transaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NEW-PORTFOLIO-LOCATION-CODE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>new_portfolio_location_code</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Default to 200000</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>If the Account is in a Location that uses Customer Portfolio processing, the ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NEW-PORTFOLIO-ID</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>new_portfolio_id</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Select CONTACT-ID from contact-account.txt where ACCT-NUM = ILMAST-KEY AND NAME-RELATIONSHIP = 'A' [since we need to create only one Transaction 200 and that's for Primary Account holder]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>If the Account is in a Location that uses Customer Portfolio processing, the ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NEW-PORTFOLIO-CONTACT-ID</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>new_portfolio_contact_id</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Select CONTACT-ID from contact-account.txt where ACCT-NUM = ILMAST-KEY AND NAME-RELATIONSHIP = 'A' [since we need to create only one Transaction 200 and that's for Primary Account holder]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>If the Account is in a Location that uses Customer Portfolio processing, the ...</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6197,7 +6312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6875,7 +6990,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7665,7 +7780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7975,7 +8090,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8605,7 +8720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8871,7 +8986,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9383,7 +9498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9497,7 +9612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9595,120 +9710,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Field Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Target Name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Transformation</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Valid Values</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TODO_FIELD_1_CDSTRANS_EFB</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>todo_field_1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>TODO(mapping-pending): CDSTRANS_EFB layout not yet authored. Replace this row with real fields before onboarding.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10181,6 +10182,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Target Name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Valid Values</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TODO_FIELD_1_CDSTRANS_EFB</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>todo_field_1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TODO(mapping-pending): CDSTRANS_EFB layout not yet authored. Replace this row with real fields before onboarding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10279,7 +10394,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10393,7 +10508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10497,7 +10612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10611,7 +10726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10715,7 +10830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10829,7 +10944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10933,7 +11048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11047,7 +11162,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11145,120 +11260,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Field Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Target Name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Transformation</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Valid Values</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TODO_FIELD_1_CDSTRANS_EST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>todo_field_1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>TODO(mapping-pending): CDSTRANS_EST layout not yet authored. Replace this row with real fields before onboarding.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11644,6 +11645,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Target Name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Valid Values</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TODO_FIELD_1_CDSTRANS_EST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>todo_field_1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TODO(mapping-pending): CDSTRANS_EST layout not yet authored. Replace this row with real fields before onboarding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -11742,7 +11857,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11856,7 +11971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11960,7 +12075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12074,7 +12189,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12178,7 +12293,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12292,7 +12407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12396,7 +12511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12510,7 +12625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12608,120 +12723,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Field Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Target Name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Transformation</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Valid Values</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TODO_FIELD_1_CONTACT</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>todo_field_1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>TODO(mapping-pending): CONTACT layout not yet authored. Replace this row with real fields before onboarding.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13150,6 +13151,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Target Name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Valid Values</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TODO_FIELD_1_CONTACT</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>todo_field_1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TODO(mapping-pending): CONTACT layout not yet authored. Replace this row with real fields before onboarding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13248,7 +13363,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13362,7 +13477,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13466,7 +13581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13580,7 +13695,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13684,7 +13799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14734,7 +14849,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17282,7 +17397,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18016,7 +18131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19080,7 +19195,178 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>rule_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>record_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>trailer_field</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>count_of</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>allow_empty_batch</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>header_field</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>detail_field</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>sum_field</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>sum_of</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>when_type</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>requires_type</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>expected_order</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CT001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>header_trailer_count</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>batch_header</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ITM-CNT-BRT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ITM-CNT-BRT ({header_value}) does not match actual detail record count ({actual_count})</t>
+        </is>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20490,230 +20776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>record_type_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>key_columns</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>staging_table</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>predicate</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ignored_fields</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>assertions</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>expected_sql_override</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>batch_header</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BK-NUM-BRT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>header.ITM-CNT-BRT == sum(detail_row_counts)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>expected_batch_header.sql</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>rt_32000</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LN-NUM-ERT</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>expected_32000.sql</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>rt_32005</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LN-NUM-ERT|CONTACT-ID</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CIF-REF-NUM-CUS|CIF-ACT-COD-CUS</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>expected_32005.sql</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>rt_32010</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LN-NUM-ERT</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CHG_OFF_CD = '1'</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>expected_32010.sql</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>rt_32025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LN-NUM-ERT</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LN-OFC-CUR-COD</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>expected_32025.sql</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>rt_32040</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LN-NUM-ERT</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>expected_32040.sql</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>rt_32075</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LN-NUM-ERT</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>expected_32075.sql</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23031,7 +23094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25368,7 +25431,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28206,7 +28269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30992,7 +31055,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34124,7 +34187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37430,7 +37493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39016,7 +39079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40770,7 +40833,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -42772,106 +42835,215 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Field Name</t>
+          <t>record_type_name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Data Type</t>
+          <t>key_columns</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>staging_table</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>predicate</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Target Name</t>
+          <t>ignored_fields</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>assertions</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Transformation</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Valid Values</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
+          <t>expected_sql_override</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TODO_FIELD_1_COLLATERAL_MASTER</t>
+          <t>batch_header</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>todo_field_1</t>
-        </is>
-      </c>
+          <t>BK-NUM-BRT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>TODO(mapping-pending): COLLATERAL_MASTER layout not yet authored. Replace this row with real fields before onboarding.</t>
+          <t>header.ITM-CNT-BRT == sum(detail_row_counts)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>expected_batch_header.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rt_32000</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LN-NUM-ERT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>expected_32000.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rt_32005</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LN-NUM-ERT|CONTACT-ID</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CIF-REF-NUM-CUS|CIF-ACT-COD-CUS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>expected_32005.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rt_32010</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LN-NUM-ERT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CHG_OFF_CD = '1'</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>expected_32010.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rt_32025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LN-NUM-ERT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LN-OFC-CUR-COD</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>expected_32025.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rt_32040</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LN-NUM-ERT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>expected_32040.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rt_32075</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LN-NUM-ERT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>expected_32075.sql</t>
         </is>
       </c>
     </row>
@@ -42956,7 +43128,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TODO_FIELD_1_FEE_MASTER</t>
+          <t>TODO_FIELD_1_COLLATERAL_MASTER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -42985,7 +43157,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>TODO(mapping-pending): FEE_MASTER layout not yet authored. Replace this row with real fields before onboarding.</t>
+          <t>TODO(mapping-pending): COLLATERAL_MASTER layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
     </row>
@@ -43070,7 +43242,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TODO_FIELD_1_LOAN_MASTER</t>
+          <t>TODO_FIELD_1_FEE_MASTER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -43099,7 +43271,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>TODO(mapping-pending): LOAN_MASTER layout not yet authored. Replace this row with real fields before onboarding.</t>
+          <t>TODO(mapping-pending): FEE_MASTER layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
     </row>

--- a/templates/SHAW_onboarding.xlsx
+++ b/templates/SHAW_onboarding.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -511,6 +511,7 @@
     <col width="21" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="27" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -599,6 +600,11 @@
           <t>gate_mr_report_blocking</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>expected_table_strategy</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -661,6 +667,11 @@
       </c>
       <c r="Q2" t="b">
         <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ctas</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/templates/SHAW_onboarding.xlsx
+++ b/templates/SHAW_onboarding.xlsx
@@ -685,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -698,6 +698,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -751,6 +756,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -787,6 +817,13 @@
           <t>TODO(mapping-pending): LOAN_MASTER layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -799,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -812,6 +849,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -865,6 +907,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -901,6 +968,13 @@
           <t>TODO(mapping-pending): LOANS_NAME layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -913,7 +987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -926,6 +1000,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -979,6 +1058,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1015,6 +1119,13 @@
           <t>TODO(mapping-pending): POSTED_TRANS layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1027,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1040,6 +1151,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1093,6 +1209,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1129,6 +1270,13 @@
           <t>TODO(mapping-pending): TRANS_MASTER layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1141,7 +1289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1154,6 +1302,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1207,6 +1360,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1247,6 +1425,13 @@
           <t>Location Code for Account</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1283,6 +1468,13 @@
           <t>Account Number</t>
         </is>
       </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1323,6 +1515,13 @@
           <t>Type of Transaction</t>
         </is>
       </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1363,6 +1562,13 @@
           <t>Date of Transaction</t>
         </is>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1403,6 +1609,13 @@
           <t>Contains up to 20 entries (days of the month) that specify the billing cycles...</t>
         </is>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1957,7 +2170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1970,6 +2183,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2023,6 +2241,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2063,6 +2306,13 @@
           <t>Location Code for Account</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2099,6 +2349,13 @@
           <t>Account Number</t>
         </is>
       </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2139,6 +2396,13 @@
           <t>Type of Transaction</t>
         </is>
       </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2179,6 +2443,13 @@
           <t>Date of Transaction</t>
         </is>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2219,6 +2490,13 @@
           <t>Current collections control indicator</t>
         </is>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2259,6 +2537,13 @@
           <t>If the Account is in a Location that uses Customer Portfolio processing, the ...</t>
         </is>
       </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2295,6 +2580,13 @@
           <t>If the Account is in a Location that uses Customer Portfolio processing, the ...</t>
         </is>
       </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2331,6 +2623,13 @@
           <t>If the Account is in a Location that uses Customer Portfolio processing, the ...</t>
         </is>
       </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3003,7 +3302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3016,6 +3315,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3069,6 +3373,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3109,6 +3438,13 @@
           <t>Location Code for Account</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3145,6 +3481,13 @@
           <t>Account Number</t>
         </is>
       </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3185,6 +3528,13 @@
           <t>Type of Transaction</t>
         </is>
       </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3225,6 +3575,13 @@
           <t>Date of Transaction</t>
         </is>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3265,6 +3622,13 @@
           <t>The total currency amount of the transaction.</t>
         </is>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3309,6 +3673,13 @@
           <t>The number of debits in the day. This field must be numeric and is used only ...</t>
         </is>
       </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3349,6 +3720,13 @@
           <t>Type of credit/debit</t>
         </is>
       </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3385,6 +3763,13 @@
           <t>The unique identifier of the outside collection agency or other third party.</t>
         </is>
       </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3429,6 +3814,13 @@
           <t>For payments and payment reversals this is the commission amount, for expense...</t>
         </is>
       </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3465,6 +3857,13 @@
           <t>The information describing the batch.</t>
         </is>
       </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3501,6 +3900,13 @@
           <t>The original transaction associated with the account.</t>
         </is>
       </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3537,6 +3943,13 @@
           <t>Used to indicate how this transaction affects the Third Party.</t>
         </is>
       </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3573,6 +3986,13 @@
           <t>An indicator specifying if commissions or expense were withheld by the third ...</t>
         </is>
       </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3617,6 +4037,13 @@
           <t>An optional field that can be used for the General Ledger mapping of Third Pa...</t>
         </is>
       </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3653,6 +4080,13 @@
           <t>An optional field that can be used to identify the Third Party Expense transa...</t>
         </is>
       </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4827,7 +5261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4840,6 +5274,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4893,6 +5332,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4933,6 +5397,13 @@
           <t>Location Code for Account</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4969,6 +5440,13 @@
           <t>Account Number</t>
         </is>
       </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5009,6 +5487,13 @@
           <t>Type of Transaction</t>
         </is>
       </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5053,6 +5538,13 @@
           <t>Date of Transaction</t>
         </is>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5093,6 +5585,13 @@
           <t>If the Account is in a Location that uses Customer Portfolio processing, the ...</t>
         </is>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5129,6 +5628,13 @@
           <t>If the Account is in a Location that uses Customer Portfolio processing, the ...</t>
         </is>
       </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5165,6 +5671,13 @@
           <t>If the Account is in a Location that uses Customer Portfolio processing, the ...</t>
         </is>
       </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5989,7 +6502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6002,6 +6515,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6055,6 +6573,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6095,6 +6638,13 @@
           <t>Location Code for Account</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6131,6 +6681,13 @@
           <t>Account Number</t>
         </is>
       </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6171,6 +6728,13 @@
           <t>Type of Transaction</t>
         </is>
       </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6211,6 +6775,13 @@
           <t>Date of Transaction</t>
         </is>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6251,6 +6822,13 @@
           <t>The currency amount of the no good check.</t>
         </is>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6287,6 +6865,13 @@
           <t>ID of the third party providing the transaction</t>
         </is>
       </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6331,6 +6916,13 @@
           <t>The amount of commission or expense the Third Party believes they are due for...</t>
         </is>
       </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6367,6 +6959,13 @@
           <t>The information describing the batch.</t>
         </is>
       </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6403,6 +7002,13 @@
           <t>The original transaction.</t>
         </is>
       </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6439,6 +7045,13 @@
           <t>Indicates if the third party withheld money from the transaction</t>
         </is>
       </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6483,6 +7096,13 @@
           <t>An optional field that can be used for the General Ledger mapping of Third Pa...</t>
         </is>
       </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6519,6 +7139,13 @@
           <t>An optional field that can be used to identify the Third Party Expense transa...</t>
         </is>
       </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6555,6 +7182,13 @@
           <t>Used to indicate how this transaction affects the Third Party.</t>
         </is>
       </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7345,7 +7979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7358,6 +7992,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7411,6 +8050,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7451,6 +8115,13 @@
           <t>Location Code for Account</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7487,6 +8158,13 @@
           <t>Account Number</t>
         </is>
       </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7527,6 +8205,13 @@
           <t>Type of Transaction</t>
         </is>
       </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7567,6 +8252,13 @@
           <t>Date of Transaction</t>
         </is>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7607,6 +8299,13 @@
           <t>The currency amount to be written off. [dropped 1 value(s) longer than length=18: +000000000000000000]</t>
         </is>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8237,7 +8936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8250,6 +8949,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8303,6 +9007,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8343,6 +9072,13 @@
           <t>Location Code for Account</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8379,6 +9115,13 @@
           <t>Account Number</t>
         </is>
       </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8419,6 +9162,13 @@
           <t>Type of Transaction</t>
         </is>
       </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8459,6 +9209,13 @@
           <t>Date of Transaction</t>
         </is>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8971,7 +9728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8984,6 +9741,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9037,6 +9799,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9073,6 +9860,13 @@
           <t>TODO(mapping-pending): CDSTRANS_EAC_COLLATERAL layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9649,7 +10443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9662,6 +10456,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9715,6 +10514,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9751,6 +10575,13 @@
           <t>TODO(mapping-pending): CDSTRANS_EFB layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9867,7 +10698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9880,6 +10711,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9933,6 +10769,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9969,6 +10830,13 @@
           <t>TODO(mapping-pending): CDSTRANS_EFI layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10085,7 +10953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10098,6 +10966,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10151,6 +11024,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10187,6 +11085,13 @@
           <t>TODO(mapping-pending): CDSTRANS_EFW_FEE_WAIVERS layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10303,7 +11208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10316,6 +11221,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10369,6 +11279,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10405,6 +11340,13 @@
           <t>TODO(mapping-pending): CDSTRANS_EFX layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10521,7 +11463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10534,6 +11476,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10587,6 +11534,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10623,6 +11595,13 @@
           <t>TODO(mapping-pending): CDSTRANS_ESA layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11112,7 +12091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11125,6 +12104,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11178,6 +12162,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11214,6 +12223,13 @@
           <t>TODO(mapping-pending): CDSTRANS_EST layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11330,7 +12346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11343,6 +12359,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11396,6 +12417,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11432,6 +12478,13 @@
           <t>TODO(mapping-pending): CDSTRANS_HSS layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11548,7 +12601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11561,6 +12614,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11614,6 +12672,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11650,6 +12733,13 @@
           <t>TODO(mapping-pending): CDSTRANS_RLT layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11766,7 +12856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11779,6 +12869,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11832,6 +12927,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11868,6 +12988,13 @@
           <t>TODO(mapping-pending): CDSTRANS_SEC layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11984,7 +13111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11997,6 +13124,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12050,6 +13182,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12086,6 +13243,13 @@
           <t>TODO(mapping-pending): CDSTRANS_XPR layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12618,7 +13782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12631,6 +13795,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12684,6 +13853,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12720,6 +13914,13 @@
           <t>TODO(mapping-pending): CONTACT layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12836,7 +14037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12849,6 +14050,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12902,6 +14108,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12938,6 +14169,13 @@
           <t>TODO(mapping-pending): CONTACT_ACCOUNT layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13054,7 +14292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13067,6 +14305,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13120,6 +14363,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13156,6 +14424,13 @@
           <t>TODO(mapping-pending): P327 layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13272,7 +14547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13285,6 +14560,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13338,6 +14618,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13378,6 +14683,19 @@
           <t>A number, defined on the Bank Control Operation tables, which identifies the bank</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TRIM(t.BK_NUM_BRT)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13418,6 +14736,19 @@
           <t>The application for which all the transactions in the batch are applicable.</t>
         </is>
       </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TRIM(t.APP_BRT)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13458,6 +14789,13 @@
           <t>The posting date for the batch.</t>
         </is>
       </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13498,6 +14836,15 @@
           <t>The transaction code for the batch.</t>
         </is>
       </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13538,6 +14885,13 @@
           <t>The number identifying the batch.</t>
         </is>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13578,6 +14932,13 @@
           <t>The source of the batch.</t>
         </is>
       </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13620,6 +14981,19 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>The type of batch. Enter 32 for NAS and EAS Batches.</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>TRIM(t.BAT_TYP_BRT)</t>
         </is>
       </c>
     </row>
@@ -13658,6 +15032,13 @@
           <t>The operator ID submitting the batch.</t>
         </is>
       </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13698,6 +15079,13 @@
           <t>The first organizational control level for GL suspense.</t>
         </is>
       </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13738,6 +15126,13 @@
           <t>The second organizational control level for GL suspense.</t>
         </is>
       </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13778,6 +15173,13 @@
           <t>The third organizational control level for GL suspense.</t>
         </is>
       </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13818,6 +15220,13 @@
           <t>The fourth organizational control level for GL suspense.</t>
         </is>
       </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13858,6 +15267,13 @@
           <t>The fifth organizational control level for GL suspense.</t>
         </is>
       </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13898,6 +15314,13 @@
           <t>The sixth organizational control level for GL suspense.</t>
         </is>
       </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13938,6 +15361,13 @@
           <t>The seventh organizational control level for GL suspense.</t>
         </is>
       </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13978,6 +15408,13 @@
           <t>The eighth organizational control level for GL suspense.</t>
         </is>
       </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14018,6 +15455,13 @@
           <t>The ninth organizational control level for GL suspense.</t>
         </is>
       </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14058,6 +15502,13 @@
           <t>The tenth organizational control level for GL suspense.</t>
         </is>
       </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14098,6 +15549,13 @@
           <t>The eleventh organizational control level for GL suspense.</t>
         </is>
       </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14138,6 +15596,13 @@
           <t>The twelfth organizational control level for GL suspense.</t>
         </is>
       </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14178,6 +15643,15 @@
           <t>The number of transactions in the batch. Used for cross-type count reconciliation.</t>
         </is>
       </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14218,6 +15692,13 @@
           <t>The total dollar amount of all transactions in the batch. Enter 0.00 for NAS and EAS Batches.</t>
         </is>
       </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16770,7 +18251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16783,6 +18264,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16836,6 +18322,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16880,6 +18391,19 @@
           <t>A number, defined on the Bank Control Operation tables, which identifies the ...</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TRIM(t.BK_NUM_ERT)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16922,6 +18446,19 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>The application to which the account is to be associated.</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TRIM(t.APP_ERT)</t>
         </is>
       </c>
     </row>
@@ -16960,6 +18497,15 @@
           <t>The account number that is associated with the account.</t>
         </is>
       </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16996,6 +18542,13 @@
           <t>The applicable reference number for the transaction.</t>
         </is>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17032,6 +18585,13 @@
           <t>Filler for account key</t>
         </is>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17072,6 +18632,15 @@
           <t>The date the transaction was effective.</t>
         </is>
       </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17114,6 +18683,19 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>The transaction code for the transaction.</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>TRIM(t.TRN_COD_ERT)</t>
         </is>
       </c>
     </row>
@@ -17156,6 +18738,13 @@
           <t>The sequential number for this item within the batch.</t>
         </is>
       </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17196,6 +18785,13 @@
           <t>The source of the transaction.</t>
         </is>
       </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17236,6 +18832,13 @@
           <t>The total number of transactions in the batch.</t>
         </is>
       </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17272,6 +18875,13 @@
           <t>Indicates if more data is available.</t>
         </is>
       </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17308,6 +18918,13 @@
           <t>The selection indicator for the account.</t>
         </is>
       </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17348,6 +18965,15 @@
           <t>The APPS location code for the location in which the account currently resides.</t>
         </is>
       </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17384,6 +19010,13 @@
           <t>The user/operator id.</t>
         </is>
       </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18623,7 +20256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18636,6 +20269,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18689,6 +20327,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18729,6 +20392,19 @@
           <t>A number, defined on the Bank Control Operation tables, which identifies the ... [Valid Values column contains prose,...</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TRIM(t.BK_NUM_ERT)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18767,6 +20443,19 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>The application to which the account is to be associated. [Valid Values column contains prose, not a list: 'Applicati...</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TRIM(t.APP_ERT)</t>
         </is>
       </c>
     </row>
@@ -18805,6 +20494,15 @@
           <t>The account number that is associated with the account.</t>
         </is>
       </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18841,6 +20539,13 @@
           <t>The applicable reference number for the transaction.</t>
         </is>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18877,6 +20582,13 @@
           <t>Filler for account key</t>
         </is>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18917,6 +20629,15 @@
           <t>The date the transaction was effective.</t>
         </is>
       </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18959,6 +20680,19 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>The transaction code for the transaction.</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>TRIM(t.TRN_COD_ERT)</t>
         </is>
       </c>
     </row>
@@ -19001,6 +20735,13 @@
           <t>The sequential number for this item within the batch.</t>
         </is>
       </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19041,6 +20782,13 @@
           <t>The source of the transaction.</t>
         </is>
       </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19081,6 +20829,13 @@
           <t>The total number of transactions in the batch.</t>
         </is>
       </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -19117,6 +20872,13 @@
           <t>Indicates if more data is available.</t>
         </is>
       </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19153,6 +20915,13 @@
           <t>Customer reference number pointing to the set of demographics data associated...</t>
         </is>
       </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -19189,6 +20958,13 @@
           <t>The relationship of the contact to the primary accountholder. [dropped 5 value(s) longer than length=1: Primary,Secon...</t>
         </is>
       </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19229,6 +21005,13 @@
           <t>Indicates whether a credit bureau report interface extract record may be crea...</t>
         </is>
       </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -19265,6 +21048,15 @@
           <t>Indicates the bankruptcy status of the contact as that status applies to the ... [Valid Values column contains prose,...</t>
         </is>
       </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>8</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -19305,6 +21097,13 @@
           <t>The date the Bankruptcy Status was recorded.</t>
         </is>
       </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19341,6 +21140,13 @@
           <t>Description of the relationship of the contact to the primary accountholder.</t>
         </is>
       </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19377,6 +21183,13 @@
           <t>APPS Enterprise supplied reference number used to keep multiple instances of ...</t>
         </is>
       </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -19413,6 +21226,13 @@
           <t>Indicates the bankruptcy status last reported to the credit bureau for the co... [Valid Values column contains prose,...</t>
         </is>
       </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -19453,6 +21273,15 @@
           <t>Indicates the current ECOA code for the contact as that status applies to the...</t>
         </is>
       </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -19493,6 +21322,13 @@
           <t>Indicates the previous ECOA code for the contact as that status applies to th...</t>
         </is>
       </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -19533,6 +21369,13 @@
           <t>The date the account was last reported to the credit bureau.</t>
         </is>
       </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -19573,6 +21416,13 @@
           <t>Indicates whether the final reporting to credit bureau has been completed for...</t>
         </is>
       </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -19613,6 +21463,13 @@
           <t>The bureau segment on which this contact was reported to credit bureau.</t>
         </is>
       </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -19653,6 +21510,13 @@
           <t>The date the account was last reported to the ChexSystems.</t>
         </is>
       </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -19689,6 +21553,13 @@
           <t>The desired action for processing the Contact-Account transaction.</t>
         </is>
       </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -19725,6 +21596,15 @@
           <t>Unique identifier for the Contact.</t>
         </is>
       </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -19761,6 +21641,13 @@
           <t>The APPS Location for the Contact-Account relationship.</t>
         </is>
       </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -19797,6 +21684,13 @@
           <t>The Account Number for the Contact-Account relationship.</t>
         </is>
       </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -19833,6 +21727,13 @@
           <t>The Name Relationship for the contact on the Account, e.g., Primary, Secondar... [dropped 7 value(s) longer than leng...</t>
         </is>
       </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -19873,6 +21774,13 @@
           <t>Indicates that the relationship between the contact and the account is the Le...</t>
         </is>
       </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -19913,6 +21821,13 @@
           <t>Indicates that the contact is a responsible party on the account. This is use...</t>
         </is>
       </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -19949,6 +21864,13 @@
           <t>Indicates that this is a Legal contact.</t>
         </is>
       </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -19985,6 +21907,13 @@
           <t>The ID of the system providing the contact account information.</t>
         </is>
       </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -20021,6 +21950,13 @@
           <t>The preferred currency for the contact for the account.</t>
         </is>
       </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22303,7 +24239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22316,6 +24252,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22369,6 +24310,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22413,6 +24379,19 @@
           <t>A number, defined on the Bank Control Operation tables, which identifies the ...</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TRIM(t.BK_NUM_ERT)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22455,6 +24434,19 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>The application to which the account is to be associated.</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TRIM(t.APP_ERT)</t>
         </is>
       </c>
     </row>
@@ -22493,6 +24485,15 @@
           <t>The account number that is associated with the account.</t>
         </is>
       </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22529,6 +24530,13 @@
           <t>The applicable reference number for the transaction.</t>
         </is>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22565,6 +24573,13 @@
           <t>Filler for account key</t>
         </is>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22605,6 +24620,15 @@
           <t>The date the transaction was effective.</t>
         </is>
       </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22647,6 +24671,19 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>The transaction code for the transaction.</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>TRIM(t.TRN_COD_ERT)</t>
         </is>
       </c>
     </row>
@@ -22689,6 +24726,13 @@
           <t>The sequential number for this item within the batch.</t>
         </is>
       </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22729,6 +24773,13 @@
           <t>The source of the transaction.</t>
         </is>
       </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22769,6 +24820,13 @@
           <t>The total number of transactions in the batch.</t>
         </is>
       </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22805,6 +24863,13 @@
           <t>Indicates if more data is available.</t>
         </is>
       </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22845,6 +24910,15 @@
           <t>The date the original contract was executed.</t>
         </is>
       </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -22885,6 +24959,13 @@
           <t>Total number of payment intervals for the account. Typically the original ter...</t>
         </is>
       </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -22925,6 +25006,13 @@
           <t>The date on which the original promissory note was to mature.</t>
         </is>
       </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -22965,6 +25053,15 @@
           <t>For Revolving Credit, Line of Credit, and Open/Demand Portfolio Type accounts...</t>
         </is>
       </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -23005,6 +25102,13 @@
           <t>Indicates the portfolio type for the account.</t>
         </is>
       </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -23045,6 +25149,13 @@
           <t>Indicates the Loan Type associated with the account.</t>
         </is>
       </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -23089,6 +25200,13 @@
           <t>The type of Charge Off Account.</t>
         </is>
       </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -23129,6 +25247,19 @@
           <t>The date the bank charged-off the account.</t>
         </is>
       </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>CHG_OFF_CD = '1'</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -23169,6 +25300,15 @@
           <t>The amount of principal included in the charge-off.</t>
         </is>
       </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -23209,6 +25349,15 @@
           <t>The amount of interest that has accrued and is due after the charge off.</t>
         </is>
       </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>8</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -23253,6 +25402,13 @@
           <t>The interest rate at which the account accrues interest.</t>
         </is>
       </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -23293,6 +25449,13 @@
           <t>The interest rate prior to charge-off.</t>
         </is>
       </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -23333,6 +25496,13 @@
           <t>The frequency of payments or the repayment plan used for the account prior to... [Valid Values column contains prose,...</t>
         </is>
       </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -23377,6 +25547,13 @@
           <t>The highest amount of credit utilized/revolving high balance since the accoun...</t>
         </is>
       </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -23417,6 +25594,13 @@
           <t>The total amount past due at 30 days delinquent.</t>
         </is>
       </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -23457,6 +25641,13 @@
           <t>The total amount past due at 60 days delinquent.</t>
         </is>
       </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -23497,6 +25688,13 @@
           <t>The total amount past due at 90 days delinquent.</t>
         </is>
       </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -23537,6 +25735,13 @@
           <t>The total amount past due at 120 days delinquent.</t>
         </is>
       </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -23577,6 +25782,13 @@
           <t>The number of payments received this month prior to the charge-off event. Pay...</t>
         </is>
       </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -23617,6 +25829,13 @@
           <t>The number of payments received this year prior to the charge-off event. Paym...</t>
         </is>
       </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -23657,6 +25876,13 @@
           <t>The number of payments received to date prior to the charge-off event. Paymen...</t>
         </is>
       </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -23697,6 +25923,13 @@
           <t>The dollar amount of payments paid this month prior to the charge off event. ...</t>
         </is>
       </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -23737,6 +25970,13 @@
           <t>The dollar amount of payments paid this year prior to the charge off event. P...</t>
         </is>
       </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -23777,6 +26017,13 @@
           <t>The total amount of all payments paid to date prior to the charge off event. ...</t>
         </is>
       </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -23813,6 +26060,13 @@
           <t>Filler</t>
         </is>
       </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -23849,6 +26103,15 @@
           <t>Indicates the reason the account was charged-off.</t>
         </is>
       </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>11</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -23889,6 +26152,15 @@
           <t>Indicates which set of state-level parameters apply to the account. Populate ...</t>
         </is>
       </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>15</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -23929,6 +26201,15 @@
           <t>The last date on which accruals were taken on the loan.</t>
         </is>
       </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>13</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -23973,6 +26254,13 @@
           <t>The current status of the account as it pertains to the ability to post monet...</t>
         </is>
       </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -24009,6 +26297,13 @@
           <t>The mortgage agency identifier as reported to the Credit Bureaus on the K3 se...</t>
         </is>
       </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -24049,6 +26344,15 @@
           <t>The date the last payment was made on the account prior to charge-off.</t>
         </is>
       </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>14</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -24085,6 +26389,13 @@
           <t>The mortgage identification number as reported to the Credit Bureaus on the K...</t>
         </is>
       </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -24125,6 +26436,13 @@
           <t>The last date that a statement was produced for the account prior to charge-off.</t>
         </is>
       </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -24165,6 +26483,13 @@
           <t>The last payment amount paid on the account prior to charge-off.</t>
         </is>
       </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -24201,6 +26526,13 @@
           <t>The original loan account number.</t>
         </is>
       </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -24241,6 +26573,15 @@
           <t>The amount of the original payment on the payment schedule.</t>
         </is>
       </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>12</v>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -24281,6 +26622,13 @@
           <t>Date the account was closed to purchases or any other withdrawal activity.</t>
         </is>
       </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27119,7 +29467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27132,6 +29480,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27185,6 +29538,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27229,6 +29607,19 @@
           <t>A number, defined on the Bank Control Operation tables, which identifies the ...</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TRIM(t.BK_NUM_ERT)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27271,6 +29662,19 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>The application to which the account is to be associated.</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TRIM(t.APP_ERT)</t>
         </is>
       </c>
     </row>
@@ -27309,6 +29713,15 @@
           <t>The account number that is associated with the account.</t>
         </is>
       </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27345,6 +29758,13 @@
           <t>The applicable reference number for the transaction.</t>
         </is>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27381,6 +29801,13 @@
           <t>Filler for account key</t>
         </is>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27421,6 +29848,15 @@
           <t>The date the transaction was effective.</t>
         </is>
       </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27463,6 +29899,19 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>The transaction code for the transaction.</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>TRIM(t.TRN_COD_ERT)</t>
         </is>
       </c>
     </row>
@@ -27505,6 +29954,13 @@
           <t>The sequential number for this item within the batch.</t>
         </is>
       </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27545,6 +30001,13 @@
           <t>The source of the transaction.</t>
         </is>
       </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27585,6 +30048,13 @@
           <t>The total number of transactions in the batch.</t>
         </is>
       </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27621,6 +30091,13 @@
           <t>Indicates if more data is available.</t>
         </is>
       </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27661,6 +30138,13 @@
           <t>Indicates if accruals have been stopped or monetary activity is to continue w...</t>
         </is>
       </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -27701,6 +30185,13 @@
           <t>The date the account was placed in stop accrual status prior to charge-off.</t>
         </is>
       </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -27741,6 +30232,13 @@
           <t>The date the account was removed from a stop accrual status.</t>
         </is>
       </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -27781,6 +30279,13 @@
           <t>The amount of interest accrued while the account’s stop accrual status is Mem...</t>
         </is>
       </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27821,6 +30326,15 @@
           <t>Indicates the account’s legal status.</t>
         </is>
       </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -27865,6 +30379,15 @@
           <t>The date of the last repossession/voluntary surrender on the account prior to...</t>
         </is>
       </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>8</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -27907,6 +30430,19 @@
       <c r="J19" t="inlineStr">
         <is>
           <t>Vehicle Collateral Status, related to repossession / voluntary surrender.</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>7</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>TRIM(TO_CHAR(t.RPO_COD_COD))</t>
         </is>
       </c>
     </row>
@@ -27949,6 +30485,15 @@
           <t>The cycle ID used to control processing in APPS Enterprise.</t>
         </is>
       </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -27989,6 +30534,13 @@
           <t>The date the account was removed from repossession/surrender status prior to ...</t>
         </is>
       </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -28025,6 +30577,13 @@
           <t>Real Estate Collateral Status</t>
         </is>
       </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -28069,6 +30628,13 @@
           <t>Organization control level 1 for the bank that the account resides in.</t>
         </is>
       </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -28113,6 +30679,13 @@
           <t>Organization control level 2 for the bank that the account resides in.</t>
         </is>
       </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -28157,6 +30730,13 @@
           <t>Organization control level 3 for the bank that the account resides in.</t>
         </is>
       </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -28197,6 +30777,13 @@
           <t>Organization control level 4 for the bank that the account resides in.</t>
         </is>
       </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -28241,6 +30828,13 @@
           <t>Organization control level 5 for the bank that the account resides in.</t>
         </is>
       </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -28281,6 +30875,23 @@
           <t>Organization control level 6 for the bank that the account resides in.</t>
         </is>
       </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>10</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>ORG_LVL_NUM6_COD</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>TRIM(t.ORG_LVL_NUM6_COD)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -28321,6 +30932,13 @@
           <t>Organization control level 7 for the bank that the account resides in.</t>
         </is>
       </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -28361,6 +30979,13 @@
           <t>Organization control level 8 for the bank that the account resides in.</t>
         </is>
       </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -28401,6 +31026,13 @@
           <t>Organization control level 9 for the bank that the account resides in.</t>
         </is>
       </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -28441,6 +31073,13 @@
           <t>Organization control level 10 for the bank that the account resides in.</t>
         </is>
       </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -28481,6 +31120,13 @@
           <t>Organization control level 11 for the bank that the account resides in.</t>
         </is>
       </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -28521,6 +31167,13 @@
           <t>Organization control level 12 for the bank that the account resides in.</t>
         </is>
       </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -28557,6 +31210,13 @@
           <t>Indicates if form 1098 for mortgage interest reporting and Regulation C compl...</t>
         </is>
       </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -28593,6 +31253,15 @@
           <t>A numeric code for location of record for lease sales-use tax liability. Comp...</t>
         </is>
       </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>11</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -28629,6 +31298,13 @@
           <t>The behavioral score developed for this account.</t>
         </is>
       </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -28665,6 +31341,13 @@
           <t>The federal Call Report code.</t>
         </is>
       </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -28705,6 +31388,13 @@
           <t>A number identifying a pool of securitized loans to which the account belonge...</t>
         </is>
       </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -28741,6 +31431,15 @@
           <t>The loan officer originally assigned to the loan account.</t>
         </is>
       </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>12</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -28777,6 +31476,13 @@
           <t>The loan officer currently assigned to the loan account.</t>
         </is>
       </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -28817,6 +31523,13 @@
           <t>The original branch number.</t>
         </is>
       </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -28857,6 +31570,13 @@
           <t>Identifies the purpose of the loan.</t>
         </is>
       </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -28897,6 +31617,13 @@
           <t>Indicates the associated category for the account.</t>
         </is>
       </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -28937,6 +31664,13 @@
           <t>A number to indicate the dealer associated with an indirect recovery loan.</t>
         </is>
       </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -28977,6 +31711,13 @@
           <t>The date the account was placed in Real Estate Collateral Status.</t>
         </is>
       </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -29017,6 +31758,13 @@
           <t>Frequency that a statement should be generated</t>
         </is>
       </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -29057,6 +31805,13 @@
           <t>The currency (non-Euro) of the nation associated with borrowers of this account.</t>
         </is>
       </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -29097,6 +31852,13 @@
           <t>The currency (national or base), which the borrower prefers to use in dealing...</t>
         </is>
       </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -29137,6 +31899,13 @@
           <t>The currency (Euro or national) in which this account is being maintained.</t>
         </is>
       </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -29177,6 +31946,13 @@
           <t>The bank associated with the partial charge off account being combined with t...</t>
         </is>
       </c>
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -29217,6 +31993,13 @@
           <t>The application associated with the partial charge off account being combined...</t>
         </is>
       </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -29253,6 +32036,13 @@
           <t>The account number for the partial charge off account being combined with the...</t>
         </is>
       </c>
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -29297,6 +32087,13 @@
           <t>The source of the input data.</t>
         </is>
       </c>
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -29333,6 +32130,13 @@
           <t>The HMDA Unique Loan Identifier.</t>
         </is>
       </c>
+      <c r="K55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -29369,6 +32173,13 @@
           <t>The IRS Property Security Type, used to identify the property address that is...</t>
         </is>
       </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -29405,6 +32216,13 @@
           <t>The IRS Property Address or Description. Field may also be used in determinat...</t>
         </is>
       </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -29449,6 +32267,13 @@
           <t>The IRS number of mortgaged properties.</t>
         </is>
       </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -32573,7 +35398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -32586,6 +35411,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32639,6 +35469,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32683,6 +35538,19 @@
           <t>A number, defined on the Bank Control Operation tables, which identifies the ...</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TRIM(t.BK_NUM_ERT)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32725,6 +35593,19 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>The application to which the account is to be associated.</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TRIM(t.APP_ERT)</t>
         </is>
       </c>
     </row>
@@ -32763,6 +35644,15 @@
           <t>The account number that is associated with the account.</t>
         </is>
       </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32799,6 +35689,13 @@
           <t>The applicable reference number for the transaction.</t>
         </is>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32835,6 +35732,13 @@
           <t>Filler for account key</t>
         </is>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32875,6 +35779,15 @@
           <t>The date the transaction was effective.</t>
         </is>
       </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32917,6 +35830,19 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>The transaction code for the transaction.</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>TRIM(t.TRN_COD_ERT)</t>
         </is>
       </c>
     </row>
@@ -32959,6 +35885,13 @@
           <t>The sequential number for this item within the batch.</t>
         </is>
       </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32999,6 +35932,13 @@
           <t>The source of the transaction.</t>
         </is>
       </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -33039,6 +35979,13 @@
           <t>The total number of transactions in the batch.</t>
         </is>
       </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33075,6 +36022,13 @@
           <t>Indicates if more data is available.</t>
         </is>
       </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33115,6 +36069,15 @@
           <t>The date the account went delinquent leading to the charge-off.</t>
         </is>
       </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33155,6 +36118,13 @@
           <t>Special comment codes for reporting the current account to the credit bureaus.</t>
         </is>
       </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33195,6 +36165,13 @@
           <t>The highest number of days delinquent.</t>
         </is>
       </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -33231,6 +36208,13 @@
           <t>Indicates if currently the account is in compliance for specified reasons.</t>
         </is>
       </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -33271,6 +36255,15 @@
           <t>The highest total dollar amount delinquent.</t>
         </is>
       </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -33307,6 +36300,15 @@
           <t>The account number used to identify the account to the credit bureau when it ...</t>
         </is>
       </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>8</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -33347,6 +36349,13 @@
           <t>The delinquency history profile for the current month.</t>
         </is>
       </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -33387,6 +36396,13 @@
           <t>The delinquency history profile for 12 months ago.</t>
         </is>
       </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -33427,6 +36443,13 @@
           <t>The delinquency history profile for 23 months ago.</t>
         </is>
       </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -33467,6 +36490,13 @@
           <t>The delinquency history profile for 2 months ago.</t>
         </is>
       </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -33507,6 +36537,13 @@
           <t>The delinquency history profile for 13 months ago.</t>
         </is>
       </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -33547,6 +36584,13 @@
           <t>The delinquency history profile for 24 months ago.</t>
         </is>
       </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -33587,6 +36631,13 @@
           <t>The delinquency history profile for 3 months ago.</t>
         </is>
       </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -33627,6 +36678,13 @@
           <t>The delinquency history profile for 14 months ago.</t>
         </is>
       </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -33667,6 +36725,13 @@
           <t>The delinquency history profile for 25 months ago.</t>
         </is>
       </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -33707,6 +36772,13 @@
           <t>The delinquency history profile for 4 months ago.</t>
         </is>
       </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -33747,6 +36819,13 @@
           <t>The delinquency history profile for 15 months ago.</t>
         </is>
       </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -33787,6 +36866,13 @@
           <t>The delinquency history profile for 5 months ago.</t>
         </is>
       </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -33827,6 +36913,13 @@
           <t>The delinquency history profile for 16 months ago.</t>
         </is>
       </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -33867,6 +36960,13 @@
           <t>The delinquency history profile for 6 months ago.</t>
         </is>
       </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -33907,6 +37007,13 @@
           <t>The delinquency history profile for 17 months ago.</t>
         </is>
       </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -33947,6 +37054,13 @@
           <t>The delinquency history profile for 7 months ago.</t>
         </is>
       </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -33987,6 +37101,13 @@
           <t>The delinquency history profile for 18 months ago.</t>
         </is>
       </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -34027,6 +37148,13 @@
           <t>The delinquency history profile for 8 months ago.</t>
         </is>
       </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -34067,6 +37195,13 @@
           <t>The delinquency history profile for 19 months ago.</t>
         </is>
       </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -34107,6 +37242,13 @@
           <t>The delinquency history profile for 9 months ago.</t>
         </is>
       </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -34147,6 +37289,13 @@
           <t>The delinquency history profile for 20 months ago.</t>
         </is>
       </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -34187,6 +37336,13 @@
           <t>The delinquency history profile for 10 months ago.</t>
         </is>
       </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -34227,6 +37383,13 @@
           <t>The delinquency history profile for 21 months ago.</t>
         </is>
       </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -34267,6 +37430,13 @@
           <t>The delinquency history profile for 11 months ago.</t>
         </is>
       </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -34307,6 +37477,13 @@
           <t>The delinquency history profile for 22 months ago.</t>
         </is>
       </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -34343,6 +37520,15 @@
           <t>The original type of account, such as installment loan, charge cards, commerc...</t>
         </is>
       </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>9</v>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -34383,6 +37569,13 @@
           <t>The loan balance at the time of the last report to the credit bureau.</t>
         </is>
       </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -34427,6 +37620,13 @@
           <t>The date the account was last reported to the credit bureau.</t>
         </is>
       </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -34467,6 +37667,13 @@
           <t>The account status at the time of the last report to the credit bureau.</t>
         </is>
       </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -34507,6 +37714,13 @@
           <t>The special comment codes reported to the credit bureau the last time the acc...</t>
         </is>
       </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -34543,6 +37757,13 @@
           <t>The compliance code reported to the credit bureau the last time the account w...</t>
         </is>
       </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -34583,6 +37804,13 @@
           <t>The current metro 2 payment rating being reported to the credit bureau.</t>
         </is>
       </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -34623,6 +37851,13 @@
           <t>The petition date when bankruptcy is filed.</t>
         </is>
       </c>
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -34659,6 +37894,13 @@
           <t>The metro 2 account status code at bankruptcy filing.</t>
         </is>
       </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -34699,6 +37941,13 @@
           <t>The scheduled monthly payment amount at bankruptcy filing.</t>
         </is>
       </c>
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -34739,6 +37988,13 @@
           <t>The current account balance at bankruptcy filing.</t>
         </is>
       </c>
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -34779,6 +38035,13 @@
           <t>The amount past due on account at bankruptcy filing.</t>
         </is>
       </c>
+      <c r="K55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -34815,6 +38078,13 @@
           <t>The metro 2 payment rating at bankruptcy filing.</t>
         </is>
       </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -34851,6 +38121,13 @@
           <t>The numeric bank code and check digit code assigned by the American Bankers A...</t>
         </is>
       </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -34887,6 +38164,13 @@
           <t>The account number reported in this field should match the account number in ...</t>
         </is>
       </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -34923,6 +38207,13 @@
           <t>This code defines the account type to be reported to ChexSystems.</t>
         </is>
       </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -34959,6 +38250,13 @@
           <t>Closure Reason Code 1 describes the primary reason for the account closure.</t>
         </is>
       </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -34995,6 +38293,13 @@
           <t>Closure Reason Code 2 describes the secondary reason for the account closure.</t>
         </is>
       </c>
+      <c r="K61" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -35031,6 +38336,13 @@
           <t>Describes the third reason for the account closure.</t>
         </is>
       </c>
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -35067,6 +38379,13 @@
           <t>This is a notification that the consumer is disputing information reported to...</t>
         </is>
       </c>
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -35107,6 +38426,13 @@
           <t>Date account was last reported to bureau via Chex Systems format.</t>
         </is>
       </c>
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -35143,6 +38469,13 @@
           <t>The last reason the account was reported to ChexSystems.</t>
         </is>
       </c>
+      <c r="K65" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -35179,6 +38512,13 @@
           <t>The last closure status reported to ChexSystems.</t>
         </is>
       </c>
+      <c r="K66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -35219,6 +38559,13 @@
           <t>The date the second plan account was last reported to the credit bureau.</t>
         </is>
       </c>
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -35255,6 +38602,13 @@
           <t>The account number used to identify the second plan account to the credit bur...</t>
         </is>
       </c>
+      <c r="K68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -35291,6 +38645,13 @@
           <t>The account status at the time of the last report to the credit bureau for th...</t>
         </is>
       </c>
+      <c r="K69" t="b">
+        <v>0</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -35331,6 +38692,13 @@
           <t>The loan balance at the time of the last report to the credit bureau for the ...</t>
         </is>
       </c>
+      <c r="K70" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -36925,7 +40293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -36938,6 +40306,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36991,6 +40364,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37035,6 +40433,19 @@
           <t>A number, defined on the Bank Control Operation tables, which identifies the ...</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TRIM(t.BK_NUM_ERT)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37077,6 +40488,19 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>The application to which the account is to be associated.</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TRIM(t.APP_ERT)</t>
         </is>
       </c>
     </row>
@@ -37115,6 +40539,15 @@
           <t>The account number that is associated with the account.</t>
         </is>
       </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37151,6 +40584,13 @@
           <t>The applicable reference number for the transaction.</t>
         </is>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37187,6 +40627,13 @@
           <t>Filler for account key</t>
         </is>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37227,6 +40674,15 @@
           <t>The date the transaction was effective.</t>
         </is>
       </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37269,6 +40725,19 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>The transaction code for the transaction.</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>TRIM(t.TRN_COD_ERT)</t>
         </is>
       </c>
     </row>
@@ -37311,6 +40780,13 @@
           <t>The sequential number for this item within the batch.</t>
         </is>
       </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37351,6 +40827,13 @@
           <t>The source of the transaction.</t>
         </is>
       </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -37391,6 +40874,13 @@
           <t>The total number of transactions in the batch.</t>
         </is>
       </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -37427,6 +40917,13 @@
           <t>Indicates if more data is available.</t>
         </is>
       </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -37467,6 +40964,15 @@
           <t>The reference number associated with the cost for the account.</t>
         </is>
       </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37503,6 +41009,13 @@
           <t>A free form field for maintaining a generic description of the cost.</t>
         </is>
       </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37543,6 +41056,13 @@
           <t>The cost amount to be assessed.</t>
         </is>
       </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -37583,6 +41103,13 @@
           <t>The percentage used when calculating a recovery cost amount.</t>
         </is>
       </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37627,6 +41154,13 @@
           <t>Indicates how the recovery cost is to be assessed.</t>
         </is>
       </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37671,6 +41205,13 @@
           <t>Indicates whether to include payments made against this cost as interest repo...</t>
         </is>
       </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -37711,6 +41252,13 @@
           <t>The total amount permitted to be assessed on an account associated with a spe...</t>
         </is>
       </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -37755,6 +41303,13 @@
           <t>A code summarizing the category with which the cost is associated. [dropped 1 value(s) longer than length=3: &lt;spaces&gt;]</t>
         </is>
       </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -37795,6 +41350,13 @@
           <t>The recovery costs maximum amount life to date; used to validate the calculat...</t>
         </is>
       </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -37831,6 +41393,13 @@
           <t>Not used</t>
         </is>
       </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -37871,6 +41440,13 @@
           <t>The original charge-off amount of the recovery cost.</t>
         </is>
       </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -37911,6 +41487,15 @@
           <t>Indicates whether the amount due is included in the calculated payoff. If inc...</t>
         </is>
       </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>8</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -37955,6 +41540,13 @@
           <t>Indicates when a recovery cost is to be capitalized.</t>
         </is>
       </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -37991,6 +41583,13 @@
           <t>Not used</t>
         </is>
       </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -38031,6 +41630,13 @@
           <t>Payment posting priority to negotiate relative payment allocation for costs w...</t>
         </is>
       </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -38071,6 +41677,15 @@
           <t>The cost’s due amount.</t>
         </is>
       </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -38111,6 +41726,13 @@
           <t>The total foreclosure cost paid from the beginning of the current year to the...</t>
         </is>
       </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -38151,6 +41773,13 @@
           <t>The amount capitalized for the recovery cost since charge-off.</t>
         </is>
       </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -38191,6 +41820,13 @@
           <t>The amount assessed this month for the recovery cost since charge-off.</t>
         </is>
       </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -38231,6 +41867,13 @@
           <t>The amount recovered for the cost this month since charge-off.</t>
         </is>
       </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -38271,6 +41914,13 @@
           <t>The amount assessed this year for the recovery cost since charge-off.</t>
         </is>
       </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -38311,6 +41961,13 @@
           <t>The amount recovered for the cost this year since charge-off.</t>
         </is>
       </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -38351,6 +42008,13 @@
           <t>The amount assessed for the recovery cost since charge-off.</t>
         </is>
       </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -38391,6 +42055,13 @@
           <t>The amount recovered for the recovery cost since charge-off.</t>
         </is>
       </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40391,7 +44062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40401,6 +44072,7 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40439,6 +44111,11 @@
           <t>expected_sql_override</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>cardinality</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40464,6 +44141,7 @@
           <t>expected_batch_header.sql</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40485,6 +44163,7 @@
           <t>expected_32000.sql</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40510,6 +44189,11 @@
           <t>expected_32005.sql</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>many_per_driver_row</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40535,6 +44219,11 @@
           <t>expected_32010.sql</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>zero_or_one_per_driver_row</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40560,6 +44249,7 @@
           <t>expected_32025.sql</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40581,6 +44271,7 @@
           <t>expected_32040.sql</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40602,6 +44293,7 @@
           <t>expected_32075.sql</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40614,7 +44306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -40627,6 +44319,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40680,6 +44377,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40716,6 +44438,13 @@
           <t>TODO(mapping-pending): COLLATERAL_MASTER layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40728,7 +44457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -40741,6 +44470,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40794,6 +44528,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40830,6 +44589,13 @@
           <t>TODO(mapping-pending): FEE_MASTER layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
